--- a/data/fmsForecastOutput/File1/RPT_RPT8588219622925VG_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT8588219622925VG_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>300.740960079141</v>
+        <v>203.1406627850367</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>332.8206552358941</v>
+        <v>289.5414489036987</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>366.1755790260343</v>
+        <v>318.3454734885776</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>394.3661134487203</v>
+        <v>341.4322490025465</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>427.3040520808261</v>
+        <v>370.5112832573205</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>37.56934345616632</v>
+        <v>25.37686029889629</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>43.1861760718652</v>
+        <v>37.57034846168268</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>49.49052905518452</v>
+        <v>43.0260421712961</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>56.04289913634197</v>
+        <v>48.5205306445079</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>64.36174721438672</v>
+        <v>55.8074594354069</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>47424598.08329054</v>
+        <v>32033761.82751574</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>55410467.85654644</v>
+        <v>48205022.42039336</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>64457296.43036576</v>
+        <v>56037840.11620143</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>74042493.58908696</v>
+        <v>64104126.20598</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>86570106.42502302</v>
+        <v>75064116.68006122</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>352.291852048476</v>
+        <v>237.9616009075152</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>389.8704220475512</v>
+        <v>339.172599742452</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>428.9428113684871</v>
+        <v>372.9140068483762</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>461.9655681602156</v>
+        <v>399.9581544147842</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>500.5494956714866</v>
+        <v>434.0217114064876</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>46.26989379859481</v>
+        <v>31.25379692465686</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>53.17241563229732</v>
+        <v>46.25800118376986</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>60.91527445543132</v>
+        <v>52.95847948347807</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>68.95211170070426</v>
+        <v>59.69700176713459</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>79.14764948921312</v>
+        <v>68.62817480022871</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>47424598.08329054</v>
+        <v>32033761.82751574</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>55410467.85654644</v>
+        <v>48205022.42039336</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>64457296.43036576</v>
+        <v>56037840.11620143</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>74042493.58908696</v>
+        <v>64104126.20598</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>86570106.42502302</v>
+        <v>75064116.68006122</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>550.1991098219373</v>
+        <v>375.1385142805241</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>606.8032727787472</v>
+        <v>527.8958616163919</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>665.8009218871561</v>
+        <v>578.8333679221212</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>709.0525545580731</v>
+        <v>613.8797217681538</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>759.9475633607692</v>
+        <v>658.9431891584778</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>62.44396997308113</v>
+        <v>42.57574704012237</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>70.04254821614126</v>
+        <v>60.9343637371077</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>79.43263813965828</v>
+        <v>69.05707088388533</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>89.2194424891711</v>
+        <v>77.24393090396286</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>101.8920496610899</v>
+        <v>88.3496117240641</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>17686936.99423293</v>
+        <v>12059363.8698127</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>20003703.48836537</v>
+        <v>17402464.2948157</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>22877617.30630274</v>
+        <v>19889321.02693155</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>25913592.39658751</v>
+        <v>22435331.18690372</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>29941550.96793959</v>
+        <v>25962029.53255464</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>556.9930772043903</v>
+        <v>379.7707988197495</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>614.2961995560346</v>
+        <v>534.4144240806503</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>674.0223632994702</v>
+        <v>585.9809167845884</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>717.8080756814562</v>
+        <v>621.4600299365766</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>769.3315461147918</v>
+        <v>667.0799499312844</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>62.72131460770862</v>
+        <v>42.76484704468527</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>70.35484150852272</v>
+        <v>61.20604707181318</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>79.78952239896927</v>
+        <v>69.36733857950499</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>89.62545070962466</v>
+        <v>77.59544252578186</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>102.3631664549142</v>
+        <v>88.75811254379937</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>17686936.99423293</v>
+        <v>12059363.8698127</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>20003703.48836537</v>
+        <v>17402464.2948157</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>22877617.30630274</v>
+        <v>19889321.02693155</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>25913592.39658751</v>
+        <v>22435331.18690372</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>29941550.96793959</v>
+        <v>25962029.53255464</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>342.9830243778948</v>
+        <v>232.2659662061156</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>378.1046296252325</v>
+        <v>328.9367770368027</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>415.1107394508189</v>
+        <v>360.8886601933423</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>445.6407889586574</v>
+        <v>385.8245517351084</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>481.462022131731</v>
+        <v>417.4711246244777</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>42.12793791789213</v>
+        <v>28.52877696357821</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>48.07572374059458</v>
+        <v>41.82406768363873</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>54.91278158565105</v>
+        <v>47.74003245532305</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>62.02199844996661</v>
+        <v>53.6970814668716</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>71.09090516440456</v>
+        <v>61.64224542187434</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>65111535.07752347</v>
+        <v>44093125.69732843</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>75414171.3449118</v>
+        <v>65607486.71520906</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>87334913.7366685</v>
+        <v>75927161.14313298</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>99956085.98567449</v>
+        <v>86539457.39288372</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>116511657.3929626</v>
+        <v>101026146.2126158</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>391.3618938429027</v>
+        <v>265.0278350497149</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>431.7054311111228</v>
+        <v>375.5674541190533</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>474.0998535894215</v>
+        <v>412.1725715554925</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>508.9981653037589</v>
+        <v>440.6777696925184</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>549.9229457771861</v>
+        <v>476.8329381701344</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>49.81951886167651</v>
+        <v>33.73746763508004</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>56.85557935566415</v>
+        <v>49.46221115660277</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>64.93923638439674</v>
+        <v>56.45682413263677</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>73.33766865071357</v>
+        <v>63.4939032366817</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>84.04608084902564</v>
+        <v>72.87555462208927</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>65111535.07752347</v>
+        <v>44093125.69732843</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>75414171.3449118</v>
+        <v>65607486.71520906</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>87334913.7366685</v>
+        <v>75927161.14313298</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>99956085.98567449</v>
+        <v>86539457.39288372</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>116511657.3929626</v>
+        <v>101026146.2126158</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="AS10" s="154" t="n">
-        <v>0.980726167491445</v>
+        <v>0.7855555</v>
       </c>
       <c r="AT10" s="154" t="n">
         <v>0.9490429845289819</v>
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>702.1079318055075</v>
+        <v>479.7508916801084</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>762.2386050884729</v>
+        <v>663.11876490906</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>824.7878903133743</v>
+        <v>717.0533898859611</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>874.1644087084682</v>
+        <v>756.8295275660014</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>928.448942169601</v>
+        <v>805.0492630476101</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>120.2709688986606</v>
+        <v>82.18124587196176</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>135.8075512270153</v>
+        <v>118.1474344566022</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>154.4106326223431</v>
+        <v>134.2413835807157</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>174.4523311576863</v>
+        <v>151.0364344024572</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>198.8771666116091</v>
+        <v>172.4445030262374</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>8225347.283844909</v>
+        <v>5620386.147263004</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>9454913.551621262</v>
+        <v>8225417.283798292</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>10954992.05560249</v>
+        <v>9524041.613485556</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>12634093.1797238</v>
+        <v>10938279.66133091</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>14786148.15626932</v>
+        <v>12820928.68639722</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>892.991300076529</v>
+        <v>610.1816445408989</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>969.4698095435131</v>
+        <v>843.4020770261272</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1049.024483407125</v>
+        <v>912.0000071953663</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1111.825086216868</v>
+        <v>962.5901562164452</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1180.868055130275</v>
+        <v>1023.919479425111</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>138.863788892117</v>
+        <v>94.88573412317751</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>156.9221372500337</v>
+        <v>136.5163259187776</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>178.5973718321608</v>
+        <v>155.2688302059298</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>202.0565921774845</v>
+        <v>174.9355083275657</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>230.7232762699949</v>
+        <v>200.0579623635992</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>8225347.283844909</v>
+        <v>5620386.147263004</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>9454913.551621262</v>
+        <v>8225417.283798292</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>10954992.05560249</v>
+        <v>9524041.613485556</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>12634093.1797238</v>
+        <v>10938279.66133091</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>14786148.15626932</v>
+        <v>12820928.68639722</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>363.8569495207904</v>
+        <v>246.6508827114696</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>400.5954795349117</v>
+        <v>348.502963346382</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>439.4384161359094</v>
+        <v>382.0386324882375</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>471.5815058937588</v>
+        <v>408.2833722434443</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>509.0617527638311</v>
+        <v>441.4025904903312</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>45.43918653984222</v>
+        <v>30.80225754792907</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>51.8039677140126</v>
+        <v>45.06749872063974</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>59.16172002266089</v>
+        <v>51.43397068434496</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>66.85700661818849</v>
+        <v>57.88310987396065</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>76.63628460615122</v>
+        <v>66.45059144013713</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>73336882.3613684</v>
+        <v>49713511.84459144</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>84869084.89653306</v>
+        <v>73832903.99900736</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>98289905.792271</v>
+        <v>85451202.75661854</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>112590179.1653983</v>
+        <v>97477737.05421463</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>131297805.5492319</v>
+        <v>113847074.8990131</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>417.6771936160774</v>
+        <v>283.1344808159791</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>460.1406367978277</v>
+        <v>400.3050051046792</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>504.9439166498963</v>
+        <v>438.9877541805959</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>541.9725763321791</v>
+        <v>469.226185426832</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>585.1309027967666</v>
+        <v>507.3614249512514</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>53.68019002332777</v>
+        <v>36.38865842966863</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>61.20358017222117</v>
+        <v>53.24480716105555</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>69.89701636445885</v>
+        <v>60.76701436732606</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>78.98379982598009</v>
+        <v>68.38218153707096</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>90.52716552661114</v>
+        <v>78.4952417977693</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>73336882.3613684</v>
+        <v>49713511.84459144</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>84869084.89653306</v>
+        <v>73832903.99900736</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>98289905.792271</v>
+        <v>85451202.75661854</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>112590179.1653983</v>
+        <v>97477737.05421463</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>131297805.5492319</v>
+        <v>113847074.8990131</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>3209.812768059381</v>
+        <v>2489.932521250425</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>3305.9118784958</v>
+        <v>2829.880057524482</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>3479.547699358202</v>
+        <v>2976.67600387986</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>3625.884961160802</v>
+        <v>3088.071294818668</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>3840.484076832168</v>
+        <v>3275.296348110885</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>2820.330162583948</v>
+        <v>2187.80106502192</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>2903.88716527619</v>
+        <v>2485.744532929125</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>3058.99814380203</v>
+        <v>2616.905171970502</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>3187.531147187758</v>
+        <v>2714.736827673556</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>3388.721821267638</v>
+        <v>2890.018024789378</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>69181528.77413526</v>
+        <v>53665852.43808048</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>78576830.33966155</v>
+        <v>67262230.00924897</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>91552316.14418441</v>
+        <v>78320979.07905753</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>105696187.4316451</v>
+        <v>90018675.68212728</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>125113292.9968061</v>
+        <v>106700901.0985346</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>2333.953299674143</v>
+        <v>1810.506295497071</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>2403.829909964541</v>
+        <v>2057.69257436611</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>2530.085840240638</v>
+        <v>2164.43240878395</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>2636.492151053575</v>
+        <v>2245.43134100889</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>2792.533749215437</v>
+        <v>2381.568418928618</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>2040.878803226025</v>
+        <v>1583.161035014338</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>2101.321035605943</v>
+        <v>1798.743194517217</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>2213.628355424478</v>
+        <v>1893.710038323504</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>2306.637641970869</v>
+        <v>1964.502891299138</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>2452.545577101909</v>
+        <v>2091.614861968981</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>69181528.77413526</v>
+        <v>53665852.43808048</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>78576830.33966155</v>
+        <v>67262230.00924897</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>91552316.14418441</v>
+        <v>78320979.07905753</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>105696187.4316451</v>
+        <v>90018675.68212728</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>125113292.9968061</v>
+        <v>106700901.0985346</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="AS13" s="154" t="n">
-        <v>0.9657</v>
+        <v>0.867</v>
       </c>
       <c r="AT13" s="154" t="n">
         <v>0.9340000000000001</v>
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>638.7886600278506</v>
+        <v>463.361646109511</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>693.6670163280271</v>
+        <v>598.8099518086739</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>759.4199686674211</v>
+        <v>655.1327935883223</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>814.803413092572</v>
+        <v>699.8729211623344</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>882.6584700370881</v>
+        <v>759.2048088699231</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>86.98175081777943</v>
+        <v>63.09443132358731</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>98.1460842042068</v>
+        <v>84.72487601275692</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>112.2459606771624</v>
+        <v>96.83180956707047</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>127.1173298495465</v>
+        <v>109.1870450499088</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>146.505599389834</v>
+        <v>126.0144884560603</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>142518411.1355036</v>
+        <v>103379364.2826719</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>163445915.2361946</v>
+        <v>141095134.0082563</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>189842221.9364554</v>
+        <v>163772181.8356761</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>218286366.5970434</v>
+        <v>187496412.7363419</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>256411098.546038</v>
+        <v>220547975.9975477</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>694.4528293624943</v>
+        <v>503.7390709859866</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>752.756705039214</v>
+        <v>649.8192874360767</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>822.3954565696357</v>
+        <v>709.4601868873963</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>880.7865644582514</v>
+        <v>756.5489489645743</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>952.5167538995755</v>
+        <v>819.2923136616374</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>101.7930913716058</v>
+        <v>73.83821494023816</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>114.7743853696811</v>
+        <v>99.07930253899841</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>131.145560155406</v>
+        <v>113.1360258304495</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>148.3622074838849</v>
+        <v>127.4352682786835</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>170.7832965679096</v>
+        <v>146.8965680730024</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>142518411.1355036</v>
+        <v>103379364.2826719</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>163445915.2361946</v>
+        <v>141095134.0082563</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>189842221.9364554</v>
+        <v>163772181.8356761</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>218286366.5970434</v>
+        <v>187496412.7363419</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>256411098.546038</v>
+        <v>220547975.9975477</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3666,34 +3666,34 @@
         </is>
       </c>
       <c r="AS22" s="178" t="n">
-        <v>0.97222200886944</v>
+        <v>0.7755555</v>
       </c>
       <c r="AT22" s="178" t="n">
-        <v>0.949877939943838</v>
+        <v>0.9390429845289819</v>
       </c>
       <c r="AU22" s="178" t="n">
-        <v>0.943844334714395</v>
+        <v>0.932452822637531</v>
       </c>
       <c r="AV22" s="178" t="n">
-        <v>0.932019789921236</v>
+        <v>0.9169535229557469</v>
       </c>
       <c r="AW22" s="178" t="n">
-        <v>0.9296716375637419</v>
+        <v>0.916033288559604</v>
       </c>
       <c r="AX22" s="178" t="n">
-        <v>0.949183430955845</v>
+        <v>0.943359124547455</v>
       </c>
       <c r="AY22" s="178" t="n">
-        <v>0.9487365842958559</v>
+        <v>0.9440178219936239</v>
       </c>
       <c r="AZ22" s="178" t="n">
-        <v>0.947337586100609</v>
+        <v>0.943211670924014</v>
       </c>
       <c r="BA22" s="178" t="n">
-        <v>0.94373489701852</v>
+        <v>0.939015226182339</v>
       </c>
       <c r="BB22" s="178" t="n">
-        <v>0.941703088585464</v>
+        <v>0.9372355209007139</v>
       </c>
     </row>
     <row r="23" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="C23" s="85" t="n">
-        <v>201554.1614855923</v>
+        <v>201554.1614855924</v>
       </c>
       <c r="D23" s="86" t="n">
         <v>211857.3204946432</v>
@@ -3742,7 +3742,7 @@
         <v>1661376.744195786</v>
       </c>
       <c r="P23" s="86" t="n">
-        <v>1684044.573045064</v>
+        <v>1684044.573045065</v>
       </c>
       <c r="Q23" s="87" t="n">
         <v>1713259.015934774</v>
@@ -3803,34 +3803,34 @@
         </is>
       </c>
       <c r="AS23" s="178" t="n">
-        <v>0.9722</v>
+        <v>0.857</v>
       </c>
       <c r="AT23" s="178" t="n">
-        <v>0.9499</v>
+        <v>0.924</v>
       </c>
       <c r="AU23" s="178" t="n">
-        <v>0.9438</v>
+        <v>0.9175</v>
       </c>
       <c r="AV23" s="178" t="n">
-        <v>0.9319999999999999</v>
+        <v>0.902</v>
       </c>
       <c r="AW23" s="178" t="n">
-        <v>0.9297</v>
+        <v>0.901</v>
       </c>
       <c r="AX23" s="178" t="n">
-        <v>0.9492</v>
+        <v>0.9284</v>
       </c>
       <c r="AY23" s="178" t="n">
-        <v>0.9487</v>
+        <v>0.9289999999999999</v>
       </c>
       <c r="AZ23" s="178" t="n">
-        <v>0.9473</v>
+        <v>0.9282</v>
       </c>
       <c r="BA23" s="178" t="n">
-        <v>0.9437</v>
+        <v>0.924</v>
       </c>
       <c r="BB23" s="178" t="n">
-        <v>0.9417</v>
+        <v>0.9222</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" thickBot="1">
@@ -3870,7 +3870,7 @@
         <v>4343.01680614511</v>
       </c>
       <c r="M24" s="79" t="n">
-        <v>24529.58511451443</v>
+        <v>24529.58511451442</v>
       </c>
       <c r="N24" s="80" t="n">
         <v>27059.18855224806</v>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="T24" s="79" t="n">
-        <v>29641.35091468801</v>
+        <v>29641.350914688</v>
       </c>
       <c r="U24" s="80" t="n">
         <v>32688.18231021205</v>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="C25" s="91" t="n">
-        <v>223107.2967533425</v>
+        <v>223107.2967533424</v>
       </c>
       <c r="D25" s="92" t="n">
         <v>235625.9003079122</v>
@@ -3954,7 +3954,7 @@
         <v>267900.6531999434</v>
       </c>
       <c r="G25" s="93" t="n">
-        <v>290498.6551992912</v>
+        <v>290498.6551992913</v>
       </c>
       <c r="H25" s="91" t="n">
         <v>1415379.0500445</v>
@@ -4007,7 +4007,7 @@
         <v>269193.2687759019</v>
       </c>
       <c r="Y25" s="91" t="n">
-        <v>1194855.374187104</v>
+        <v>1194855.374187103</v>
       </c>
       <c r="Z25" s="92" t="n">
         <v>1206932.845514515</v>
@@ -4022,7 +4022,7 @@
         <v>1232189.499322146</v>
       </c>
       <c r="AD25" s="91" t="n">
-        <v>1400079.40828937</v>
+        <v>1400079.408289369</v>
       </c>
       <c r="AE25" s="92" t="n">
         <v>1424062.648732516</v>
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>309.2209694257514</v>
+        <v>297.5317153231277</v>
       </c>
       <c r="D35" s="149" t="n">
         <v>350.2537801471804</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>387.8149181787844</v>
+        <v>387.8149181787845</v>
       </c>
       <c r="F35" s="149" t="n">
         <v>422.9702052615251</v>
@@ -4423,7 +4423,7 @@
         <v>459.4487048068605</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>38.62868829423051</v>
+        <v>37.16843624870832</v>
       </c>
       <c r="I35" s="149" t="n">
         <v>45.44826524829572</v>
@@ -4438,13 +4438,13 @@
         <v>69.20346589917921</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>48761832.07662392</v>
+        <v>46918524.20939991</v>
       </c>
       <c r="N35" s="152" t="n">
         <v>58312864.66497568</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>68266434.39100204</v>
+        <v>68266434.39100206</v>
       </c>
       <c r="P35" s="152" t="n">
         <v>79412930.37978917</v>
@@ -4458,13 +4458,13 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>362.2254447234466</v>
+        <v>348.5325012155357</v>
       </c>
       <c r="U35" s="149" t="n">
         <v>410.2918101430514</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>454.2914132523853</v>
+        <v>454.2914132523854</v>
       </c>
       <c r="W35" s="149" t="n">
         <v>495.4727714299193</v>
@@ -4473,13 +4473,13 @@
         <v>538.2041578077308</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>47.57456853187857</v>
+        <v>45.77614191991704</v>
       </c>
       <c r="Z35" s="149" t="n">
         <v>55.95758340650192</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>64.51509475756626</v>
+        <v>64.51509475756627</v>
       </c>
       <c r="AB35" s="149" t="n">
         <v>73.95333383037939</v>
@@ -4488,13 +4488,13 @@
         <v>85.10166208170644</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>48761832.07662392</v>
+        <v>46918524.20939991</v>
       </c>
       <c r="AE35" s="152" t="n">
         <v>58312864.66497568</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>68266434.39100204</v>
+        <v>68266434.39100206</v>
       </c>
       <c r="AG35" s="152" t="n">
         <v>79412930.37978917</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>565.9086046083704</v>
+        <v>549.651884694979</v>
       </c>
       <c r="D36" s="156" t="n">
         <v>638.8115762007227</v>
@@ -4519,13 +4519,13 @@
         <v>705.4030879692488</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>760.7592100776445</v>
+        <v>760.7592100776446</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>817.4262300366822</v>
+        <v>817.4262300366823</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>64.2268940149862</v>
+        <v>62.38186353054734</v>
       </c>
       <c r="I36" s="156" t="n">
         <v>73.73722693051934</v>
@@ -4534,13 +4534,13 @@
         <v>84.15733049819283</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>95.72564424922405</v>
+        <v>95.72564424922406</v>
       </c>
       <c r="L36" s="157" t="n">
         <v>109.5986592243803</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>18191941.16370313</v>
+        <v>17669345.66016969</v>
       </c>
       <c r="N36" s="159" t="n">
         <v>21058880.08272808</v>
@@ -4549,10 +4549,10 @@
         <v>24238389.22827421</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>27803304.50143995</v>
+        <v>27803304.50143996</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>32206181.46459539</v>
+        <v>32206181.4645954</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>572.8965559382135</v>
+        <v>556.4390948333779</v>
       </c>
       <c r="U36" s="156" t="n">
         <v>646.6997478367067</v>
@@ -4569,13 +4569,13 @@
         <v>714.1135447576933</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>770.1532152057897</v>
+        <v>770.1532152057898</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>827.5199707303523</v>
+        <v>827.5199707303524</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>64.51215749937907</v>
+        <v>62.65893231966692</v>
       </c>
       <c r="Z36" s="156" t="n">
         <v>74.06599340112449</v>
@@ -4584,13 +4584,13 @@
         <v>84.53544240866007</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>96.16126004538995</v>
+        <v>96.16126004538997</v>
       </c>
       <c r="AC36" s="157" t="n">
         <v>110.1054089571904</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>18191941.16370313</v>
+        <v>17669345.66016969</v>
       </c>
       <c r="AE36" s="159" t="n">
         <v>21058880.08272808</v>
@@ -4599,10 +4599,10 @@
         <v>24238389.22827421</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>27803304.50143995</v>
+        <v>27803304.50143996</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>32206181.46459539</v>
+        <v>32206181.4645954</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,13 +4612,13 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>352.6872406269887</v>
+        <v>340.2245534468739</v>
       </c>
       <c r="D37" s="162" t="n">
         <v>397.9467468160924</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>439.6837884462557</v>
+        <v>439.6837884462558</v>
       </c>
       <c r="F37" s="162" t="n">
         <v>478.0091880397898</v>
@@ -4627,13 +4627,13 @@
         <v>517.7313269920802</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>43.31988792890257</v>
+        <v>41.78912029757072</v>
       </c>
       <c r="I37" s="162" t="n">
         <v>50.59863425200986</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>58.16341893164001</v>
+        <v>58.16341893164002</v>
       </c>
       <c r="K37" s="162" t="n">
         <v>66.52686615368154</v>
@@ -4642,13 +4642,13 @@
         <v>76.44629685405373</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>66953773.24032705</v>
+        <v>64587869.8695696</v>
       </c>
       <c r="N37" s="165" t="n">
         <v>79371744.74770376</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>92504823.61927626</v>
+        <v>92504823.61927627</v>
       </c>
       <c r="P37" s="165" t="n">
         <v>107216234.8812291</v>
@@ -4662,13 +4662,13 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>402.4349213094808</v>
+        <v>388.2143316286122</v>
       </c>
       <c r="U37" s="162" t="n">
         <v>454.3604030021783</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>502.1648440216011</v>
+        <v>502.1648440216012</v>
       </c>
       <c r="W37" s="162" t="n">
         <v>545.9684251056387</v>
@@ -4677,13 +4677,13 @@
         <v>591.3495216092396</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>51.22909120227973</v>
+        <v>49.41884102980234</v>
       </c>
       <c r="Z37" s="162" t="n">
         <v>59.83923779340266</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>68.78340346017796</v>
+        <v>68.78340346017798</v>
       </c>
       <c r="AB37" s="162" t="n">
         <v>78.66443178681055</v>
@@ -4692,13 +4692,13 @@
         <v>90.37740666187828</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>66953773.24032705</v>
+        <v>64587869.8695696</v>
       </c>
       <c r="AE37" s="165" t="n">
         <v>79371744.74770376</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>92504823.61927626</v>
+        <v>92504823.61927627</v>
       </c>
       <c r="AG37" s="165" t="n">
         <v>107216234.8812291</v>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>722.1068685387845</v>
+        <v>702.8801848671825</v>
       </c>
       <c r="D38" s="156" t="n">
         <v>802.3898184552372</v>
@@ -4723,13 +4723,13 @@
         <v>873.7820185630105</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>937.8388397236423</v>
+        <v>937.8388397236421</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>998.5916384034791</v>
+        <v>998.5916384034792</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>123.6967833481126</v>
+        <v>120.4032557163351</v>
       </c>
       <c r="I38" s="156" t="n">
         <v>142.9612665200117</v>
@@ -4738,13 +4738,13 @@
         <v>163.5829476219391</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>187.1594979275484</v>
+        <v>187.1594979275483</v>
       </c>
       <c r="L38" s="157" t="n">
         <v>213.9019892506383</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>8459639.181838185</v>
+        <v>8234394.396597152</v>
       </c>
       <c r="N38" s="159" t="n">
         <v>9952954.78023549</v>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>918.4273843373522</v>
+        <v>893.9735069912973</v>
       </c>
       <c r="U38" s="156" t="n">
         <v>1020.537006764651</v>
@@ -4773,13 +4773,13 @@
         <v>1111.338734962794</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1192.810801315761</v>
+        <v>1192.81080131576</v>
       </c>
       <c r="X38" s="157" t="n">
         <v>1270.080574549747</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>142.8192037262081</v>
+        <v>139.0165260729261</v>
       </c>
       <c r="Z38" s="156" t="n">
         <v>165.188071529187</v>
@@ -4794,7 +4794,7 @@
         <v>248.1540168809688</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>8459639.181838185</v>
+        <v>8234394.396597152</v>
       </c>
       <c r="AE38" s="159" t="n">
         <v>9952954.78023549</v>
@@ -4816,40 +4816,40 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>374.1595403752356</v>
+        <v>361.3036998562408</v>
       </c>
       <c r="D39" s="162" t="n">
         <v>421.6266840314249</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>465.4616512575342</v>
+        <v>465.4616512575343</v>
       </c>
       <c r="F39" s="162" t="n">
         <v>505.8450185120082</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>547.4226098276001</v>
+        <v>547.4226098276002</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>46.72579477501641</v>
+        <v>45.12033159439441</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>54.52366849543198</v>
+        <v>54.52366849543199</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>62.66523563216846</v>
+        <v>62.66523563216847</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>71.71460994073431</v>
+        <v>71.71460994073429</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>82.41128841210158</v>
+        <v>82.4112884121016</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>75413412.42216524</v>
+        <v>72822264.26616675</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>89324699.52793925</v>
+        <v>89324699.52793926</v>
       </c>
       <c r="O39" s="165" t="n">
         <v>104110565.1488338</v>
@@ -4858,7 +4858,7 @@
         <v>120770599.6787372</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>141191882.886834</v>
+        <v>141191882.8868341</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,40 +4866,40 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>429.5037019203073</v>
+        <v>414.7462776176479</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>484.2979534028133</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>534.846341617108</v>
+        <v>534.8463416171081</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>581.3504653626412</v>
+        <v>581.3504653626411</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>629.2240266740073</v>
+        <v>629.2240266740074</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>55.20014184925167</v>
+        <v>53.30350647406336</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>64.41675924257697</v>
+        <v>64.41675924257699</v>
       </c>
       <c r="AA39" s="162" t="n">
         <v>74.03626870190085</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>84.72249480903662</v>
+        <v>84.7224948090366</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>97.3489305449027</v>
+        <v>97.34893054490273</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>75413412.42216524</v>
+        <v>72822264.26616675</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>89324699.52793925</v>
+        <v>89324699.52793926</v>
       </c>
       <c r="AF39" s="165" t="n">
         <v>104110565.1488338</v>
@@ -4908,7 +4908,7 @@
         <v>120770599.6787372</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>141191882.886834</v>
+        <v>141191882.8868341</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>3301.597169367806</v>
+        <v>3301.597169367807</v>
       </c>
       <c r="D40" s="156" t="n">
         <v>3480.273585109801</v>
@@ -4933,7 +4933,7 @@
         <v>4130.885314437096</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>2900.977332425373</v>
+        <v>2900.977332425374</v>
       </c>
       <c r="I40" s="156" t="n">
         <v>3057.045126093473</v>
@@ -5020,22 +5020,22 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>656.9627481758935</v>
+        <v>645.3488377672925</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>730.1653162186615</v>
+        <v>730.1653162186614</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>804.5121242644021</v>
+        <v>804.5121242644022</v>
       </c>
       <c r="F41" s="180" t="n">
         <v>874.1245058957192</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>949.2839689357264</v>
+        <v>949.2839689357262</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>89.45645662511875</v>
+        <v>87.87502864370012</v>
       </c>
       <c r="I41" s="180" t="n">
         <v>103.3101833037128</v>
@@ -5050,7 +5050,7 @@
         <v>157.5642466267223</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>146573182.8131705</v>
+        <v>143982034.657172</v>
       </c>
       <c r="N41" s="183" t="n">
         <v>172045860.0076335</v>
@@ -5070,13 +5070,13 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>714.2106111223356</v>
+        <v>701.5846622789985</v>
       </c>
       <c r="U41" s="186" t="n">
         <v>792.3640949229716</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>871.226914023882</v>
+        <v>871.2269140238822</v>
       </c>
       <c r="W41" s="186" t="n">
         <v>944.9115063650141</v>
@@ -5085,7 +5085,7 @@
         <v>1024.415348987214</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>104.689192588194</v>
+        <v>102.8384774497117</v>
       </c>
       <c r="Z41" s="186" t="n">
         <v>120.8134067421561</v>
@@ -5100,7 +5100,7 @@
         <v>183.6744914339295</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>146573182.8131705</v>
+        <v>143982034.657172</v>
       </c>
       <c r="AE41" s="189" t="n">
         <v>172045860.0076335</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="C50" s="161" t="n">
-        <v>0.08543437829440999</v>
+        <v>0.08543437829440997</v>
       </c>
       <c r="D50" s="162" t="n">
-        <v>0.09784356153829189</v>
+        <v>0.09784356153829188</v>
       </c>
       <c r="E50" s="162" t="n">
         <v>0.1117403837389542</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="T50" s="161" t="n">
-        <v>0.09807148499249578</v>
+        <v>0.09807148499249577</v>
       </c>
       <c r="U50" s="162" t="n">
         <v>0.1123871861087075</v>
@@ -5986,7 +5986,7 @@
         <v>0.07718104575580055</v>
       </c>
       <c r="D52" s="180" t="n">
-        <v>0.08797366820908517</v>
+        <v>0.08797366820908516</v>
       </c>
       <c r="E52" s="180" t="n">
         <v>0.09997933894145931</v>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="T52" s="185" t="n">
-        <v>0.08390661724635966</v>
+        <v>0.08390661724635967</v>
       </c>
       <c r="U52" s="186" t="n">
         <v>0.0954676625131157</v>
@@ -6334,46 +6334,46 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.006733567703092378</v>
+        <v>0.006760514740708186</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.00631265298990767</v>
+        <v>0.006312652989907677</v>
       </c>
       <c r="E57" s="149" t="n">
         <v>0.005913511288780401</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0002182438534425571</v>
+        <v>0.0002182438534425569</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.0008411748025817804</v>
+        <v>0.0008445410966544206</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.0008191178618692217</v>
+        <v>0.0008191178618692225</v>
       </c>
       <c r="J57" s="149" t="n">
         <v>0.0007992417272445699</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>3.101437433010643e-05</v>
+        <v>3.101437433010639e-05</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>1061.833219863857</v>
+        <v>1066.082565972643</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>1050.977606359471</v>
+        <v>1050.977606359472</v>
       </c>
       <c r="O57" s="152" t="n">
         <v>1040.945851984663</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>40.97542503859014</v>
+        <v>40.97542503859008</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6384,46 +6384,46 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.007887788335822194</v>
+        <v>0.007919354444364226</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.007394723394407922</v>
+        <v>0.00739472339440793</v>
       </c>
       <c r="V57" s="149" t="n">
         <v>0.006927163641047748</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0002556536738701703</v>
+        <v>0.00025565367387017</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.001035979476908446</v>
+        <v>0.001040125359026871</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.001008528176485709</v>
+        <v>0.00100852817648571</v>
       </c>
       <c r="AA57" s="149" t="n">
         <v>0.000983744366867618</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>3.815838645203497e-05</v>
+        <v>3.815838645203491e-05</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>1061.833219863857</v>
+        <v>1066.082565972643</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>1050.977606359471</v>
+        <v>1050.977606359472</v>
       </c>
       <c r="AF57" s="152" t="n">
         <v>1040.945851984663</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>40.97542503859014</v>
+        <v>40.97542503859008</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6538,46 +6538,46 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.005593337166758683</v>
+        <v>0.00561572112035899</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.005269294769275118</v>
+        <v>0.005269294769275124</v>
       </c>
       <c r="E59" s="162" t="n">
         <v>0.004947709728648776</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0001826834310492176</v>
+        <v>0.0001826834310492174</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.0006870187273625171</v>
+        <v>0.0006897681048552986</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.0006699869289792086</v>
+        <v>0.0006699869289792093</v>
       </c>
       <c r="J59" s="162" t="n">
         <v>0.0006545060820106302</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>2.542494259523513e-05</v>
+        <v>2.54249425952351e-05</v>
       </c>
       <c r="L59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>1061.833219863857</v>
+        <v>1066.082565972643</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>1050.977606359471</v>
+        <v>1050.977606359472</v>
       </c>
       <c r="O59" s="165" t="n">
         <v>1040.945851984663</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>40.97542503859014</v>
+        <v>40.97542503859008</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6588,46 +6588,46 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.006382295539130642</v>
+        <v>0.006407836822080715</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.00601627960037465</v>
+        <v>0.006016279600374657</v>
       </c>
       <c r="V59" s="162" t="n">
         <v>0.005650801665740215</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0002086557908057063</v>
+        <v>0.000208655790805706</v>
       </c>
       <c r="X59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.0008124523567441314</v>
+        <v>0.0008157037065758382</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.000792343662122974</v>
+        <v>0.0007923436621229749</v>
       </c>
       <c r="AA59" s="162" t="n">
         <v>0.0007740115133016669</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>3.006362358699152e-05</v>
+        <v>3.006362358699148e-05</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>1061.833219863857</v>
+        <v>1066.082565972643</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>1050.977606359471</v>
+        <v>1050.977606359472</v>
       </c>
       <c r="AF59" s="165" t="n">
         <v>1040.945851984663</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>40.97542503859014</v>
+        <v>40.97542503859008</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6742,46 +6742,46 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.005268227716249657</v>
+        <v>0.005289310615642385</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.004960780226548957</v>
+        <v>0.004960780226548962</v>
       </c>
       <c r="E61" s="162" t="n">
         <v>0.004653902074605053</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0001716246726630459</v>
+        <v>0.0001716246726630456</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.0006579068566597682</v>
+        <v>0.0006605397314738087</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.0006415152237634223</v>
+        <v>0.000641515223763423</v>
       </c>
       <c r="J61" s="162" t="n">
         <v>0.0006265561713327992</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>2.433155612057167e-05</v>
+        <v>2.433155612057163e-05</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>1061.833219863857</v>
+        <v>1066.082565972643</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>1050.977606359471</v>
+        <v>1050.977606359472</v>
       </c>
       <c r="O61" s="165" t="n">
         <v>1040.945851984663</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>40.97542503859014</v>
+        <v>40.97542503859008</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6792,46 +6792,46 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.006047482591033662</v>
+        <v>0.006071683987388032</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.005698158589079576</v>
+        <v>0.005698158589079582</v>
       </c>
       <c r="V61" s="162" t="n">
         <v>0.005347642479508114</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.0001972423957319334</v>
+        <v>0.0001972423957319331</v>
       </c>
       <c r="X61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.0007772270538377746</v>
+        <v>0.0007803374356708959</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.0007579154679050703</v>
+        <v>0.0007579154679050711</v>
       </c>
       <c r="AA61" s="162" t="n">
         <v>0.0007402490486099231</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>2.874491179446564e-05</v>
+        <v>2.87449117944656e-05</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>1061.833219863857</v>
+        <v>1066.082565972643</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>1050.977606359471</v>
+        <v>1050.977606359472</v>
       </c>
       <c r="AF61" s="165" t="n">
         <v>1040.945851984663</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>40.97542503859014</v>
+        <v>40.97542503859008</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6946,46 +6946,46 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.004759294004793454</v>
+        <v>0.004778340204405135</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.004460365371489595</v>
+        <v>0.004460365371489599</v>
       </c>
       <c r="E63" s="180" t="n">
         <v>0.004164063495649975</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0001529500751459862</v>
+        <v>0.000152950075145986</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.0006480574109995112</v>
+        <v>0.0006506508693564216</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.0006310915540558595</v>
+        <v>0.0006310915540558603</v>
       </c>
       <c r="J63" s="180" t="n">
         <v>0.0006154688139292611</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>2.386171294871138e-05</v>
+        <v>2.386171294871135e-05</v>
       </c>
       <c r="L63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>1061.833219863857</v>
+        <v>1066.082565972643</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>1050.977606359471</v>
+        <v>1050.977606359472</v>
       </c>
       <c r="O63" s="183" t="n">
         <v>1040.945851984663</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>40.97542503859014</v>
+        <v>40.97542503859008</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -6996,46 +6996,46 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.005174019819407362</v>
+        <v>0.005194725708595123</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.004840319434657624</v>
+        <v>0.00484031943465763</v>
       </c>
       <c r="V63" s="186" t="n">
         <v>0.004509371679676935</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.0001653360418682477</v>
+        <v>0.0001653360418682475</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.0007584092827714785</v>
+        <v>0.0007614443578419551</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.0007380136030496213</v>
+        <v>0.0007380136030496222</v>
       </c>
       <c r="AA63" s="186" t="n">
         <v>0.0007190993945259967</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>2.784967566269448e-05</v>
+        <v>2.784967566269443e-05</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>1061.833219863857</v>
+        <v>1066.082565972643</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>1050.977606359471</v>
+        <v>1050.977606359472</v>
       </c>
       <c r="AF63" s="189" t="n">
         <v>1040.945851984663</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>40.97542503859014</v>
+        <v>40.97542503859008</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.002858008376089825</v>
+        <v>0.002869445828360694</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.004231307705790088</v>
+        <v>0.004231307705790091</v>
       </c>
       <c r="E68" s="149" t="n">
         <v>0.005664116158427144</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.007022073357940794</v>
+        <v>0.007022073357940787</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.008333118956914243</v>
+        <v>0.00833311895691425</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.0003570298447330324</v>
+        <v>0.00035845864103838</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.0005490464510592767</v>
+        <v>0.0005490464510592771</v>
       </c>
       <c r="J68" s="149" t="n">
         <v>0.0007655346816305535</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.0009978984895167523</v>
+        <v>0.000997898489516751</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.00125515799160004</v>
+        <v>0.001255157991600041</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>450.6865261022976</v>
+        <v>452.490126705621</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>704.4597020478222</v>
+        <v>704.4597020478228</v>
       </c>
       <c r="O68" s="152" t="n">
         <v>997.0452295340147</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>1318.398827527652</v>
+        <v>1318.39882752765</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>1688.256854667008</v>
+        <v>1688.256854667009</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.003347907992705035</v>
+        <v>0.00336130597228906</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.004956608597204409</v>
+        <v>0.004956608597204412</v>
       </c>
       <c r="V68" s="149" t="n">
         <v>0.006635018958325118</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.008225747593005721</v>
+        <v>0.008225747593005711</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.009761523371804914</v>
+        <v>0.009761523371804921</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.0004397131139116245</v>
+        <v>0.0004414728000606623</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.0006760062768368359</v>
+        <v>0.0006760062768368365</v>
       </c>
       <c r="AA68" s="149" t="n">
         <v>0.0009422561473262581</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.001227759612287865</v>
+        <v>0.001227759612287864</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.001543506959838074</v>
+        <v>0.001543506959838075</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>450.6865261022976</v>
+        <v>452.490126705621</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>704.4597020478222</v>
+        <v>704.4597020478228</v>
       </c>
       <c r="AF68" s="152" t="n">
         <v>997.0452295340147</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>1318.398827527652</v>
+        <v>1318.39882752765</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>1688.256854667008</v>
+        <v>1688.256854667009</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.002374046742791254</v>
+        <v>0.002383547430940614</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.003531955201237716</v>
+        <v>0.003531955201237718</v>
       </c>
       <c r="E70" s="162" t="n">
         <v>0.004739046101834101</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.005877904160290904</v>
+        <v>0.005877904160290898</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.006976396845718798</v>
+        <v>0.006976396845718804</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.0002915995448342948</v>
+        <v>0.0002927664958845966</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.0004490854890805308</v>
+        <v>0.0004490854890805312</v>
       </c>
       <c r="J70" s="162" t="n">
         <v>0.0006269030858094164</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.0008180565418405526</v>
+        <v>0.0008180565418405516</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.001030109009122528</v>
+        <v>0.001030109009122529</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>450.6865261022976</v>
+        <v>452.490126705621</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>704.4597020478222</v>
+        <v>704.4597020478228</v>
       </c>
       <c r="O70" s="165" t="n">
         <v>997.0452295340147</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>1318.398827527652</v>
+        <v>1318.39882752765</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>1688.256854667008</v>
+        <v>1688.256854667009</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.002708913745849635</v>
+        <v>0.002719754536917031</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.004032651608436551</v>
+        <v>0.004032651608436555</v>
       </c>
       <c r="V70" s="162" t="n">
         <v>0.005412485993509829</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.006713574043369175</v>
+        <v>0.006713574043369167</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.00796839735628964</v>
+        <v>0.007968397356289647</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.0003448388347951523</v>
+        <v>0.0003462188439466677</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.0005310999746912929</v>
+        <v>0.0005310999746912933</v>
       </c>
       <c r="AA70" s="162" t="n">
         <v>0.0007413685212064236</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.0009673077472898386</v>
+        <v>0.0009673077472898374</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.001217829831591044</v>
+        <v>0.001217829831591045</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>450.6865261022976</v>
+        <v>452.490126705621</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>704.4597020478222</v>
+        <v>704.4597020478228</v>
       </c>
       <c r="AF70" s="165" t="n">
         <v>997.0452295340147</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>1318.398827527652</v>
+        <v>1318.39882752765</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>1688.256854667008</v>
+        <v>1688.256854667009</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,37 +7603,37 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.006483527712111256</v>
+        <v>0.006495048561595429</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.00969537224350284</v>
+        <v>0.009695372243502838</v>
       </c>
       <c r="E71" s="156" t="n">
         <v>0.01299893853538077</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>0.01610687589719862</v>
+        <v>0.01610687589719863</v>
       </c>
       <c r="G71" s="157" t="n">
         <v>0.01902315707875442</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.001110627190625365</v>
+        <v>0.001112600710175891</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.001727418099574824</v>
+        <v>0.001727418099574823</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>0.002433564248748223</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.003214363362248185</v>
+        <v>0.003214363362248188</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.004074829975022105</v>
+        <v>0.004074829975022104</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>75.95593873923129</v>
+        <v>76.09090799925451</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>120.2627442393418</v>
@@ -7642,7 +7642,7 @@
         <v>172.6544121934863</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>232.7888997678468</v>
+        <v>232.7888997678469</v>
       </c>
       <c r="Q71" s="160" t="n">
         <v>302.9560444208731</v>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.008246216255999028</v>
+        <v>0.008260869299915511</v>
       </c>
       <c r="U71" s="156" t="n">
         <v>0.012331270837786</v>
@@ -7662,13 +7662,13 @@
         <v>0.01653298374293271</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.02048588172280477</v>
+        <v>0.02048588172280478</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.02419501760595789</v>
+        <v>0.02419501760595788</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.001282320256909174</v>
+        <v>0.001284598864995133</v>
       </c>
       <c r="Z71" s="156" t="n">
         <v>0.001995987245632264</v>
@@ -7677,13 +7677,13 @@
         <v>0.00281475551022546</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.003722984397433852</v>
+        <v>0.003722984397433854</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.004727330633769204</v>
+        <v>0.004727330633769203</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>75.95593873923129</v>
+        <v>76.09090799925451</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>120.2627442393418</v>
@@ -7692,7 +7692,7 @@
         <v>172.6544121934863</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>232.7888997678468</v>
+        <v>232.7888997678469</v>
       </c>
       <c r="AH71" s="160" t="n">
         <v>302.9560444208731</v>
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.002612907919934835</v>
+        <v>0.002622526028779911</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.003892820150663697</v>
+        <v>0.003892820150663699</v>
       </c>
       <c r="E72" s="162" t="n">
         <v>0.005229539633518428</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.006497115909970412</v>
+        <v>0.006497115909970407</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.007720238158554327</v>
+        <v>0.007720238158554332</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.0003263051881837593</v>
+        <v>0.0003275063169310527</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.0005034093985173514</v>
+        <v>0.0005034093985173517</v>
       </c>
       <c r="J72" s="162" t="n">
         <v>0.0007040544210179799</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.0009211084742790765</v>
+        <v>0.0009211084742790757</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.001162236930065972</v>
+        <v>0.001162236930065973</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>526.642464841529</v>
+        <v>528.5810347048755</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>824.7224462871641</v>
+        <v>824.7224462871645</v>
       </c>
       <c r="O72" s="165" t="n">
         <v>1169.699641727501</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>1551.187727295498</v>
+        <v>1551.187727295497</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>1991.212899087881</v>
+        <v>1991.212899087882</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.002999398660965374</v>
+        <v>0.003010439441457807</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.004471455207496177</v>
+        <v>0.004471455207496178</v>
       </c>
       <c r="V72" s="162" t="n">
         <v>0.006009088254150194</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.007466914211959675</v>
+        <v>0.007466914211959668</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.008873874140013564</v>
+        <v>0.008873874140013571</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.0003854849930454488</v>
+        <v>0.0003869039625364775</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.0005947509204641934</v>
+        <v>0.0005947509204641937</v>
       </c>
       <c r="AA72" s="162" t="n">
         <v>0.0008318098826152079</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.001088182840221269</v>
+        <v>0.001088182840221268</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.00137290078048457</v>
+        <v>0.001372900780484571</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>526.642464841529</v>
+        <v>528.5810347048755</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>824.7224462871641</v>
+        <v>824.7224462871645</v>
       </c>
       <c r="AF72" s="165" t="n">
         <v>1169.699641727501</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>1551.187727295498</v>
+        <v>1551.187727295497</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>1991.212899087881</v>
+        <v>1991.212899087882</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.002360489650070753</v>
+        <v>0.002369178607767595</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.003500134939365451</v>
+        <v>0.003500134939365452</v>
       </c>
       <c r="E74" s="180" t="n">
         <v>0.004679113298454359</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.005790160302960493</v>
+        <v>0.005790160302960487</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.006854465118683066</v>
+        <v>0.006854465118683069</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.0003214201118433284</v>
+        <v>0.0003226032586343499</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.0004952297433767545</v>
+        <v>0.0004952297433767547</v>
       </c>
       <c r="J74" s="180" t="n">
         <v>0.0006915956769268278</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.0009033218384783037</v>
+        <v>0.0009033218384783031</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.001137719236600286</v>
+        <v>0.001137719236600287</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>526.642464841529</v>
+        <v>528.5810347048755</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>824.7224462871641</v>
+        <v>824.7224462871645</v>
       </c>
       <c r="O74" s="183" t="n">
         <v>1169.699641727501</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>1551.187727295498</v>
+        <v>1551.187727295497</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>1991.212899087881</v>
+        <v>1991.212899087882</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.002566183181932267</v>
+        <v>0.00257562929710989</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.003798292238395004</v>
+        <v>0.003798292238395006</v>
       </c>
       <c r="V74" s="186" t="n">
         <v>0.005067132385491233</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.006259050120507666</v>
+        <v>0.006259050120507661</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.007396963929085191</v>
+        <v>0.007396963929085196</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.0003761518537616276</v>
+        <v>0.0003775364679855558</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.0005791335423488615</v>
+        <v>0.0005791335423488618</v>
       </c>
       <c r="AA74" s="186" t="n">
         <v>0.00080804424412646</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.001054292299749094</v>
+        <v>0.001054292299749093</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.001326252666140793</v>
+        <v>0.001326252666140794</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>526.642464841529</v>
+        <v>528.5810347048755</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>824.7224462871641</v>
+        <v>824.7224462871645</v>
       </c>
       <c r="AF74" s="189" t="n">
         <v>1169.699641727501</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>1551.187727295498</v>
+        <v>1551.187727295497</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>1991.212899087881</v>
+        <v>1991.212899087882</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,13 +8260,13 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>309.3335021579338</v>
+        <v>297.6442864398001</v>
       </c>
       <c r="D79" s="149" t="n">
         <v>350.3822224588424</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>387.9614611168861</v>
+        <v>387.9614611168862</v>
       </c>
       <c r="F79" s="149" t="n">
         <v>423.1305178417331</v>
@@ -8275,13 +8275,13 @@
         <v>459.6288996629908</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>38.64274617601792</v>
+        <v>37.18249892558611</v>
       </c>
       <c r="I79" s="149" t="n">
         <v>45.46493167869674</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>52.43500403485943</v>
+        <v>52.43500403485944</v>
       </c>
       <c r="K79" s="149" t="n">
         <v>60.13057441862553</v>
@@ -8290,13 +8290,13 @@
         <v>69.23060735904396</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>48779577.64607866</v>
+        <v>46936275.83180135</v>
       </c>
       <c r="N79" s="152" t="n">
         <v>58334248.70010031</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>68292230.10798056</v>
+        <v>68292230.10798058</v>
       </c>
       <c r="P79" s="152" t="n">
         <v>79443029.17070328</v>
@@ -8310,13 +8310,13 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>362.3572670220327</v>
+        <v>348.66436847821</v>
       </c>
       <c r="U79" s="149" t="n">
         <v>410.4422691289005</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>454.4630755462574</v>
+        <v>454.4630755462575</v>
       </c>
       <c r="W79" s="149" t="n">
         <v>495.6605636607258</v>
@@ -8325,13 +8325,13 @@
         <v>538.4152403938176</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>47.59188202840255</v>
+        <v>45.79346132200929</v>
       </c>
       <c r="Z79" s="149" t="n">
         <v>55.9781037314067</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>64.5394729624638</v>
+        <v>64.53947296246382</v>
       </c>
       <c r="AB79" s="149" t="n">
         <v>73.98136334549382</v>
@@ -8340,13 +8340,13 @@
         <v>85.13503878207544</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>48779577.64607866</v>
+        <v>46936275.83180135</v>
       </c>
       <c r="AE79" s="152" t="n">
         <v>58334248.70010031</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>68292230.10798056</v>
+        <v>68292230.10798058</v>
       </c>
       <c r="AG79" s="152" t="n">
         <v>79443029.17070328</v>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>565.9192085784429</v>
+        <v>549.6624886650515</v>
       </c>
       <c r="D80" s="156" t="n">
         <v>638.8223657606205</v>
@@ -8371,13 +8371,13 @@
         <v>705.4139092635713</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>760.7698486938721</v>
+        <v>760.7698486938722</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>817.4365363584238</v>
+        <v>817.436536358424</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>64.22809749564799</v>
+        <v>62.38306701120912</v>
       </c>
       <c r="I80" s="156" t="n">
         <v>73.73847235601929</v>
@@ -8386,13 +8386,13 @@
         <v>84.15862152067098</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>95.72698289669464</v>
+        <v>95.72698289669465</v>
       </c>
       <c r="L80" s="157" t="n">
         <v>109.600041072678</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>18192282.0434814</v>
+        <v>17669686.53994796</v>
       </c>
       <c r="N80" s="159" t="n">
         <v>21059235.76827997</v>
@@ -8401,10 +8401,10 @@
         <v>24238761.05928575</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>27803693.30867689</v>
+        <v>27803693.3086769</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>32206587.52847742</v>
+        <v>32206587.52847743</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>572.9072908482049</v>
+        <v>556.4498297433693</v>
       </c>
       <c r="U80" s="156" t="n">
         <v>646.7106706282233</v>
@@ -8421,13 +8421,13 @@
         <v>714.1244996754975</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>770.1639851897537</v>
+        <v>770.1639851897538</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>827.5304043165924</v>
+        <v>827.5304043165925</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>64.51336632529524</v>
+        <v>62.66014114558309</v>
       </c>
       <c r="Z80" s="156" t="n">
         <v>74.06724437950679</v>
@@ -8436,13 +8436,13 @@
         <v>84.53673923159521</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>96.16260478460313</v>
+        <v>96.16260478460315</v>
       </c>
       <c r="AC80" s="157" t="n">
         <v>110.10679719472</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>18192282.0434814</v>
+        <v>17669686.53994796</v>
       </c>
       <c r="AE80" s="159" t="n">
         <v>21059235.76827997</v>
@@ -8451,10 +8451,10 @@
         <v>24238761.05928575</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>27803693.30867689</v>
+        <v>27803693.3086769</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>32206587.52847742</v>
+        <v>32206587.52847743</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,13 +8464,13 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>352.7825132242452</v>
+        <v>340.3198579287721</v>
       </c>
       <c r="D81" s="162" t="n">
         <v>398.0557434262515</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>439.8081651672143</v>
+        <v>439.8081651672144</v>
       </c>
       <c r="F81" s="162" t="n">
         <v>478.1451129027884</v>
@@ -8479,28 +8479,28 @@
         <v>517.8838621529349</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>43.33159007675604</v>
+        <v>41.80082636175272</v>
       </c>
       <c r="I81" s="162" t="n">
         <v>50.61249309029984</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>58.17987206345099</v>
+        <v>58.179872063451</v>
       </c>
       <c r="K81" s="162" t="n">
         <v>66.54578347869102</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>76.46881963291496</v>
+        <v>76.46881963291497</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>66971859.68956006</v>
+        <v>64605962.37174931</v>
       </c>
       <c r="N81" s="165" t="n">
         <v>79393484.46838029</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>92530991.16726631</v>
+        <v>92530991.16726632</v>
       </c>
       <c r="P81" s="165" t="n">
         <v>107246722.4793802</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>402.543632415989</v>
+        <v>388.3230791171944</v>
       </c>
       <c r="U81" s="162" t="n">
         <v>454.4848511704671</v>
@@ -8529,7 +8529,7 @@
         <v>591.5237463271527</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>51.24292988996589</v>
+        <v>49.43268434884748</v>
       </c>
       <c r="Z81" s="162" t="n">
         <v>59.85562760969383</v>
@@ -8544,13 +8544,13 @@
         <v>90.40403385545163</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>66971859.68956006</v>
+        <v>64605962.37174931</v>
       </c>
       <c r="AE81" s="165" t="n">
         <v>79393484.46838029</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>92530991.16726631</v>
+        <v>92530991.16726632</v>
       </c>
       <c r="AG81" s="165" t="n">
         <v>107246722.4793802</v>
@@ -8566,7 +8566,7 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>722.1684705463732</v>
+        <v>702.9417983956207</v>
       </c>
       <c r="D82" s="156" t="n">
         <v>802.4595414853076</v>
@@ -8575,13 +8575,13 @@
         <v>873.8600366281723</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>937.9245263542813</v>
+        <v>937.9245263542811</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>998.6845632146761</v>
+        <v>998.6845632146762</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>123.7073357614998</v>
+        <v>120.4138101032417</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>142.9736890264484</v>
@@ -8596,7 +8596,7 @@
         <v>213.9218940858095</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>8460360.862769058</v>
+        <v>8235116.212497285</v>
       </c>
       <c r="N82" s="159" t="n">
         <v>9953819.634386763</v>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>918.5057341954752</v>
+        <v>894.0518715024641</v>
       </c>
       <c r="U82" s="156" t="n">
         <v>1020.625685522499</v>
@@ -8631,7 +8631,7 @@
         <v>1270.198762999416</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>142.8313874486668</v>
+        <v>139.0287120739928</v>
       </c>
       <c r="Z82" s="156" t="n">
         <v>165.2024254163047</v>
@@ -8640,13 +8640,13 @@
         <v>189.223323625241</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>216.7942684772811</v>
+        <v>216.794268477281</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>248.177109068285</v>
+        <v>248.1771090682851</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>8460360.862769058</v>
+        <v>8235116.212497285</v>
       </c>
       <c r="AE82" s="159" t="n">
         <v>9953819.634386763</v>
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>374.2528558891661</v>
+        <v>361.3970460711797</v>
       </c>
       <c r="D83" s="162" t="n">
         <v>421.7333811933404</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>465.5832750829812</v>
+        <v>465.5832750829813</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>505.9779021989669</v>
+        <v>505.9779021989668</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>547.5714642776338</v>
+        <v>547.5714642776339</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>46.73744820378872</v>
+        <v>45.13198885717029</v>
       </c>
       <c r="I83" s="162" t="n">
         <v>54.5374662954907</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>62.68160988267767</v>
+        <v>62.68160988267768</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>71.73344911366074</v>
+        <v>71.73344911366073</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>82.4336975833578</v>
+        <v>82.43369758335781</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>75432220.55232911</v>
+        <v>72841078.58424661</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>89347304.10276705</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>104137768.9478334</v>
+        <v>104137768.9478335</v>
       </c>
       <c r="P83" s="165" t="n">
         <v>120802325.6856647</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>141230275.6015283</v>
+        <v>141230275.6015284</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>429.6108202865517</v>
+        <v>414.8534312260693</v>
       </c>
       <c r="U83" s="162" t="n">
         <v>484.4205102027186</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>534.9860954677594</v>
+        <v>534.9860954677595</v>
       </c>
       <c r="W83" s="162" t="n">
         <v>581.5031840618976</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>629.3951244598076</v>
+        <v>629.3951244598077</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>55.21390878300548</v>
+        <v>53.31727793716851</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>64.43306059553041</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>74.05561417149435</v>
+        <v>74.05561417149437</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>84.744751107046</v>
+        <v>84.74475110704599</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>97.37540154054204</v>
+        <v>97.37540154054207</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>75432220.55232911</v>
+        <v>72841078.58424661</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>89347304.10276705</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>104137768.9478334</v>
+        <v>104137768.9478335</v>
       </c>
       <c r="AG83" s="165" t="n">
         <v>120802325.6856647</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>141230275.6015283</v>
+        <v>141230275.6015284</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,7 +8770,7 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>3301.597169367806</v>
+        <v>3301.597169367807</v>
       </c>
       <c r="D84" s="156" t="n">
         <v>3480.273585109801</v>
@@ -8785,7 +8785,7 @@
         <v>4130.885314437096</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>2900.977332425373</v>
+        <v>2900.977332425374</v>
       </c>
       <c r="I84" s="156" t="n">
         <v>3057.045126093473</v>
@@ -8872,10 +8872,10 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>657.0470490053042</v>
+        <v>645.4331663318603</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>730.2612503871813</v>
+        <v>730.2612503871812</v>
       </c>
       <c r="E85" s="180" t="n">
         <v>804.6209467801377</v>
@@ -8884,10 +8884,10 @@
         <v>874.2429304181999</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>949.4161303554341</v>
+        <v>949.4161303554339</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>89.46793559178859</v>
+        <v>87.8865113869751</v>
       </c>
       <c r="I85" s="180" t="n">
         <v>103.3237569100109</v>
@@ -8902,7 +8902,7 @@
         <v>157.586183070622</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>146591990.9433343</v>
+        <v>144000848.9752518</v>
       </c>
       <c r="N85" s="183" t="n">
         <v>172068464.5824613</v>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>714.3022579425833</v>
+        <v>701.6763392512505</v>
       </c>
       <c r="U85" s="186" t="n">
         <v>792.4682011971577</v>
@@ -8937,7 +8937,7 @@
         <v>1024.557970364297</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>104.7026262049249</v>
+        <v>102.8519154861319</v>
       </c>
       <c r="Z85" s="186" t="n">
         <v>120.8292800429887</v>
@@ -8952,7 +8952,7 @@
         <v>183.7000630040248</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>146591990.9433343</v>
+        <v>144000848.9752518</v>
       </c>
       <c r="AE85" s="189" t="n">
         <v>172068464.5824613</v>
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="C94" s="85" t="n">
-        <v>201554.1614855923</v>
+        <v>201554.1614855924</v>
       </c>
       <c r="D94" s="86" t="n">
         <v>211857.3204946432</v>
@@ -9795,7 +9795,7 @@
         <v>1661376.744195786</v>
       </c>
       <c r="P94" s="86" t="n">
-        <v>1684044.573045064</v>
+        <v>1684044.573045065</v>
       </c>
       <c r="Q94" s="87" t="n">
         <v>1713259.015934774</v>
@@ -9898,7 +9898,7 @@
         <v>4343.01680614511</v>
       </c>
       <c r="M95" s="79" t="n">
-        <v>24529.58511451443</v>
+        <v>24529.58511451442</v>
       </c>
       <c r="N95" s="80" t="n">
         <v>27059.18855224806</v>
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="T95" s="79" t="n">
-        <v>29641.35091468801</v>
+        <v>29641.350914688</v>
       </c>
       <c r="U95" s="80" t="n">
         <v>32688.18231021205</v>
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="C96" s="132" t="n">
-        <v>223107.2967533425</v>
+        <v>223107.2967533424</v>
       </c>
       <c r="D96" s="133" t="n">
         <v>235625.9003079122</v>
@@ -10000,7 +10000,7 @@
         <v>267900.6531999434</v>
       </c>
       <c r="G96" s="134" t="n">
-        <v>290498.6551992912</v>
+        <v>290498.6551992913</v>
       </c>
       <c r="H96" s="132" t="n">
         <v>1415379.0500445</v>
@@ -10053,7 +10053,7 @@
         <v>269193.2687759019</v>
       </c>
       <c r="Y96" s="135" t="n">
-        <v>1194855.374187104</v>
+        <v>1194855.374187103</v>
       </c>
       <c r="Z96" s="136" t="n">
         <v>1206932.845514515</v>
@@ -10068,7 +10068,7 @@
         <v>1232189.499322146</v>
       </c>
       <c r="AD96" s="135" t="n">
-        <v>1400079.40828937</v>
+        <v>1400079.408289369</v>
       </c>
       <c r="AE96" s="136" t="n">
         <v>1424062.648732516</v>
